--- a/Data/FlightPlan/FPL_22AUG26.xlsx
+++ b/Data/FlightPlan/FPL_22AUG26.xlsx
@@ -455,7 +455,7 @@
     <t>14:12</t>
   </si>
   <si>
-    <t>17:53</t>
+    <t>17:43</t>
   </si>
   <si>
     <t>01:00</t>
@@ -755,7 +755,7 @@
     <t>16:30</t>
   </si>
   <si>
-    <t>21:08</t>
+    <t>20:14</t>
   </si>
   <si>
     <t>VN-A551</t>
@@ -773,6 +773,9 @@
     <t>15:05</t>
   </si>
   <si>
+    <t>17:19</t>
+  </si>
+  <si>
     <t>VN-A552</t>
   </si>
   <si>
@@ -851,6 +854,9 @@
     <t>16:00</t>
   </si>
   <si>
+    <t>16:52</t>
+  </si>
+  <si>
     <t>VN-A580</t>
   </si>
   <si>
@@ -881,9 +887,6 @@
     <t>09:35</t>
   </si>
   <si>
-    <t>17:19</t>
-  </si>
-  <si>
     <t>18:45</t>
   </si>
   <si>
@@ -932,9 +935,6 @@
     <t>15:03</t>
   </si>
   <si>
-    <t>16:03</t>
-  </si>
-  <si>
     <t>20:40</t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>08:07</t>
   </si>
   <si>
-    <t>15:38</t>
+    <t>16:17</t>
   </si>
   <si>
     <t>PXU</t>
@@ -1058,6 +1058,9 @@
     <t>15:12</t>
   </si>
   <si>
+    <t>16:48</t>
+  </si>
+  <si>
     <t>20:50</t>
   </si>
   <si>
@@ -1106,171 +1109,168 @@
     <t>12:49</t>
   </si>
   <si>
-    <t>16:06</t>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>15:14</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>14:42</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:16</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
   </si>
   <si>
     <t>VTE</t>
   </si>
   <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>08:18</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>16:21</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>15:14</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:28</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>15:56</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>14:42</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>08:16</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>14:52</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>15:37</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1325,6 +1325,9 @@
     <t>19:30</t>
   </si>
   <si>
+    <t>23:20</t>
+  </si>
+  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1385,9 +1388,6 @@
     <t>11:12</t>
   </si>
   <si>
-    <t>23:20</t>
-  </si>
-  <si>
     <t>VN-A669</t>
   </si>
   <si>
@@ -1424,9 +1424,6 @@
     <t>VN-A672</t>
   </si>
   <si>
-    <t>16:09</t>
-  </si>
-  <si>
     <t>SAI</t>
   </si>
   <si>
@@ -1520,12 +1517,12 @@
     <t>13:38</t>
   </si>
   <si>
-    <t>19:02</t>
-  </si>
-  <si>
     <t>VN-A698</t>
   </si>
   <si>
+    <t>18:42</t>
+  </si>
+  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1538,6 +1535,9 @@
     <t>14:31</t>
   </si>
   <si>
+    <t>17:02</t>
+  </si>
+  <si>
     <t>03:55</t>
   </si>
   <si>
@@ -1595,7 +1595,7 @@
     <t>Total Record(s): 394</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 22, 2026 14:52</t>
+    <t xml:space="preserve">Generated on  Aug 22, 2026 15:13</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6181,7 +6181,9 @@
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>254</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
@@ -6243,7 +6245,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6278,7 +6280,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6293,7 +6295,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6326,7 +6328,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6357,11 +6359,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6376,7 +6378,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6392,11 +6394,11 @@
         <v>8521</v>
       </c>
       <c t="s" r="C145" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6411,7 +6413,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6425,11 +6427,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C146" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6444,7 +6446,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6458,11 +6460,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C147" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6471,13 +6473,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>199</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6510,7 +6512,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6519,7 +6521,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>103</v>
@@ -6530,7 +6532,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6545,13 +6547,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
@@ -6565,7 +6567,7 @@
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6580,7 +6582,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6615,7 +6617,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6630,7 +6632,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6659,11 +6661,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6675,7 +6677,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>150</v>
@@ -6683,7 +6685,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6698,7 +6700,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6707,10 +6709,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>26</v>
@@ -6718,7 +6720,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6733,13 +6735,13 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>29</v>
@@ -6766,7 +6768,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6778,7 +6780,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>167</v>
@@ -6814,7 +6816,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6826,7 +6828,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>60</v>
@@ -6849,7 +6851,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6869,7 +6871,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6884,7 +6886,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6896,15 +6898,15 @@
         <v>55</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>247</v>
+        <v>281</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6919,7 +6921,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6963,17 +6965,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>55</v>
@@ -6982,12 +6984,12 @@
         <v>204</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6998,11 +7000,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C165" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7035,7 +7037,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7050,7 +7052,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7068,7 +7070,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7077,10 +7079,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>103</v>
@@ -7116,7 +7118,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7125,10 +7127,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>108</v>
@@ -7151,13 +7153,13 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>17</v>
@@ -7171,7 +7173,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>290</v>
+        <v>254</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7186,7 +7188,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7198,10 +7200,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7219,7 +7221,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7252,7 +7254,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7261,7 +7263,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>149</v>
@@ -7300,7 +7302,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7320,7 +7322,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7335,7 +7337,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7344,10 +7346,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>231</v>
@@ -7355,7 +7357,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7370,13 +7372,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>55</v>
@@ -7418,7 +7420,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7433,12 +7435,12 @@
         <v>176</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7453,7 +7455,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7465,7 +7467,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>103</v>
@@ -7473,7 +7475,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7488,7 +7490,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7503,7 +7505,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7523,7 +7525,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7532,18 +7534,18 @@
         <v>175</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="I182" s="7">
         <v>252</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7558,19 +7560,19 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>175</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>117</v>
@@ -7578,7 +7580,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>307</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7593,7 +7595,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7626,7 +7628,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7659,7 +7661,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7722,7 +7724,7 @@
         <v>311</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7797,7 +7799,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8159,7 +8161,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>178</v>
@@ -8311,7 +8313,7 @@
       </c>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8534,7 +8536,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8675,7 +8677,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>337</v>
@@ -9085,7 +9087,7 @@
         <v>102</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>329</v>
@@ -9117,7 +9119,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>102</v>
@@ -9130,7 +9132,9 @@
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
-      <c r="M232" s="7"/>
+      <c t="s" r="M232" s="7">
+        <v>349</v>
+      </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
@@ -9153,13 +9157,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>186</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -9183,13 +9187,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>189</v>
@@ -9222,7 +9226,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>323</v>
@@ -9258,7 +9262,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9278,7 +9282,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9293,7 +9297,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9313,7 +9317,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9328,7 +9332,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9363,7 +9367,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9383,7 +9387,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9398,7 +9402,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9407,7 +9411,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="I241" s="7">
         <v>212</v>
@@ -9416,7 +9420,7 @@
         <v>325</v>
       </c>
       <c t="s" r="K241" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
@@ -9435,13 +9439,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>55</v>
@@ -9450,7 +9454,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="K242" s="7">
         <v>186</v>
@@ -9472,7 +9476,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9487,7 +9491,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9505,7 +9509,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9520,7 +9524,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9553,7 +9557,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9565,7 +9569,7 @@
         <v>334</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>18</v>
@@ -9573,7 +9577,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9588,7 +9592,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9600,10 +9604,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9623,7 +9627,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9638,12 +9642,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9658,7 +9662,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9678,7 +9682,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>365</v>
+        <v>280</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9686,14 +9690,14 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>1831</v>
+        <v>805</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9702,13 +9706,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>366</v>
+        <v>152</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9719,29 +9723,29 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>1832</v>
+        <v>806</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
+        <v>152</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I251" s="7">
         <v>366</v>
       </c>
-      <c t="s" r="H251" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I251" s="7">
-        <v>72</v>
-      </c>
       <c t="s" r="J251" s="7">
-        <v>196</v>
+        <v>27</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9759,7 +9763,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9774,7 +9778,7 @@
         <v>198</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9960,7 +9964,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -10005,7 +10009,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>57</v>
@@ -10110,7 +10114,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>48</v>
@@ -10120,7 +10124,7 @@
       </c>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>332</v>
+        <v>375</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10217,7 +10221,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>328</v>
@@ -10253,13 +10257,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>17</v>
@@ -10273,7 +10277,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10288,7 +10292,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10300,7 +10304,7 @@
         <v>175</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>74</v>
@@ -10321,7 +10325,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10369,7 +10373,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10381,15 +10385,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10404,7 +10408,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10419,12 +10423,12 @@
         <v>227</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10439,7 +10443,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10454,12 +10458,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10474,7 +10478,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10486,7 +10490,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>189</v>
@@ -10522,7 +10526,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10557,7 +10561,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10569,7 +10573,7 @@
         <v>241</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>344</v>
@@ -10577,7 +10581,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10592,7 +10596,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10612,7 +10616,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10627,7 +10631,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10639,7 +10643,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>232</v>
@@ -10647,7 +10651,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10662,7 +10666,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10695,7 +10699,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10710,7 +10714,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10743,7 +10747,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10752,7 +10756,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>104</v>
@@ -10763,7 +10767,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10778,13 +10782,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>17</v>
@@ -10798,7 +10802,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10813,7 +10817,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10833,7 +10837,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>331</v>
+        <v>48</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10848,7 +10852,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10860,7 +10864,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>325</v>
@@ -10881,7 +10885,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10890,10 +10894,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>77</v>
@@ -10914,22 +10918,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10962,7 +10966,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10997,7 +11001,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11017,7 +11021,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11032,7 +11036,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11065,7 +11069,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11080,7 +11084,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -11113,7 +11117,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11148,7 +11152,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11160,7 +11164,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>113</v>
@@ -11168,7 +11172,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11183,7 +11187,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11192,7 +11196,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>247</v>
@@ -11216,22 +11220,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11264,7 +11268,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11273,18 +11277,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11299,13 +11303,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
@@ -11334,7 +11338,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11354,7 +11358,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11369,7 +11373,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11381,7 +11385,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>129</v>
@@ -11391,7 +11395,7 @@
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11406,7 +11410,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11439,7 +11443,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11487,7 +11491,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11496,18 +11500,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11522,13 +11526,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>17</v>
@@ -11537,12 +11541,12 @@
         <v>163</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11557,7 +11561,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11572,12 +11576,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11592,7 +11596,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11604,7 +11608,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>170</v>
@@ -11627,7 +11631,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11636,20 +11640,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K312" s="7">
         <v>112</v>
       </c>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11664,13 +11668,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>17</v>
@@ -11701,7 +11705,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11710,7 +11714,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>346</v>
@@ -11738,13 +11742,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>17</v>
@@ -11775,7 +11779,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11787,7 +11791,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>189</v>
@@ -11808,7 +11812,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11820,10 +11824,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11856,7 +11860,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11891,7 +11895,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11906,12 +11910,12 @@
         <v>46</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>418</v>
+        <v>231</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11919,14 +11923,14 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>805</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11935,13 +11939,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>152</v>
+        <v>419</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11952,29 +11956,29 @@
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>806</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>152</v>
+        <v>419</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>419</v>
+        <v>72</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12086,7 +12090,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>231</v>
@@ -12116,7 +12120,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
@@ -12239,7 +12243,7 @@
         <v>328</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12364,7 +12368,7 @@
         <v>8020</v>
       </c>
       <c t="s" r="C335" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
@@ -12397,7 +12401,7 @@
         <v>8021</v>
       </c>
       <c t="s" r="C336" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
@@ -12458,13 +12462,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>311</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12490,7 +12494,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>55</v>
@@ -12574,7 +12578,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>118</v>
+        <v>232</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12638,7 +12642,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>131</v>
@@ -12678,11 +12682,15 @@
         <v>74</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>388</v>
-      </c>
-      <c r="K344" s="7"/>
+        <v>389</v>
+      </c>
+      <c t="s" r="K344" s="7">
+        <v>75</v>
+      </c>
       <c r="L344" s="7"/>
-      <c r="M344" s="7"/>
+      <c t="s" r="M344" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="345" ht="15" customHeight="1">
       <c t="s" r="A345" s="6">
@@ -12713,9 +12721,13 @@
       <c t="s" r="J345" s="7">
         <v>144</v>
       </c>
-      <c r="K345" s="7"/>
+      <c t="s" r="K345" s="7">
+        <v>124</v>
+      </c>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>438</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c r="A346" s="6"/>
@@ -12744,7 +12756,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12764,7 +12776,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12779,7 +12791,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12814,7 +12826,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12823,7 +12835,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>157</v>
@@ -12834,7 +12846,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12849,13 +12861,13 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>55</v>
@@ -12882,7 +12894,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12897,7 +12909,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12915,7 +12927,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12927,10 +12939,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12963,7 +12975,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12983,7 +12995,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12998,7 +13010,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13018,7 +13030,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13033,7 +13045,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13066,7 +13078,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13078,7 +13090,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>71</v>
@@ -13114,7 +13126,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13126,7 +13138,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>202</v>
@@ -13134,7 +13146,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13149,7 +13161,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13161,7 +13173,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>84</v>
@@ -13169,7 +13181,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13184,7 +13196,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13204,7 +13216,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13219,7 +13231,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13254,7 +13266,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13274,7 +13286,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13289,7 +13301,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13322,7 +13334,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13334,7 +13346,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>100</v>
@@ -13355,7 +13367,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13403,7 +13415,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13418,12 +13430,12 @@
         <v>176</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13438,7 +13450,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13450,7 +13462,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>227</v>
@@ -13458,7 +13470,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13473,7 +13485,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13493,7 +13505,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13508,7 +13520,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13517,7 +13529,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>87</v>
@@ -13545,13 +13557,13 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>17</v>
@@ -13582,7 +13594,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13615,7 +13627,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13627,10 +13639,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13780,7 +13792,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>232</v>
@@ -13896,7 +13908,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>464</v>
@@ -13931,7 +13943,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>157</v>
@@ -14088,7 +14100,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>328</v>
@@ -14193,17 +14205,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>129</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>135</v>
+        <v>442</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14292,7 +14304,7 @@
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>471</v>
+        <v>232</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14316,13 +14328,13 @@
         <v>55</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14346,7 +14358,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>55</v>
@@ -14355,7 +14367,7 @@
         <v>461</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14388,7 +14400,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14408,7 +14420,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14423,7 +14435,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14443,7 +14455,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14458,7 +14470,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14473,12 +14485,12 @@
         <v>112</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14493,7 +14505,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14541,7 +14553,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -14561,7 +14573,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14576,7 +14588,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -14588,7 +14600,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>155</v>
@@ -14611,7 +14623,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -14626,14 +14638,14 @@
         <v>181</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14648,7 +14660,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -14660,7 +14672,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>117</v>
@@ -14670,7 +14682,7 @@
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14685,7 +14697,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14694,7 +14706,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>186</v>
@@ -14722,13 +14734,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>17</v>
@@ -14737,10 +14749,10 @@
         <v>198</v>
       </c>
       <c t="s" r="J409" s="7">
+        <v>478</v>
+      </c>
+      <c t="s" r="K409" s="7">
         <v>479</v>
-      </c>
-      <c t="s" r="K409" s="7">
-        <v>480</v>
       </c>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
@@ -14774,7 +14786,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14786,7 +14798,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>82</v>
@@ -14794,7 +14806,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14809,7 +14821,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14821,7 +14833,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>421</v>
@@ -14844,7 +14856,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14864,7 +14876,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -14879,7 +14891,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14891,7 +14903,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>159</v>
@@ -14914,7 +14926,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14929,7 +14941,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14947,7 +14959,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14962,7 +14974,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14980,7 +14992,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14989,7 +15001,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>430</v>
@@ -15028,7 +15040,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15048,7 +15060,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15063,7 +15075,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15075,7 +15087,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>240</v>
@@ -15083,7 +15095,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15098,7 +15110,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15133,7 +15145,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15153,7 +15165,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15168,7 +15180,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15183,7 +15195,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15216,7 +15228,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15236,7 +15248,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15251,7 +15263,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15286,7 +15298,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15306,7 +15318,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15321,7 +15333,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15354,7 +15366,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15387,7 +15399,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15399,10 +15411,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I430" s="7">
+        <v>494</v>
+      </c>
+      <c t="s" r="J430" s="7">
         <v>495</v>
-      </c>
-      <c t="s" r="J430" s="7">
-        <v>496</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15435,7 +15447,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15455,7 +15467,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15470,7 +15482,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15490,7 +15502,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15505,7 +15517,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15538,7 +15550,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15586,7 +15598,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -15606,7 +15618,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15621,7 +15633,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -15656,7 +15668,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -15671,14 +15683,14 @@
         <v>155</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="K439" s="7">
         <v>464</v>
       </c>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15693,7 +15705,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -15711,11 +15723,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K440" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15730,7 +15742,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -15752,7 +15764,7 @@
       </c>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15767,7 +15779,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -15782,7 +15794,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="K442" s="7">
         <v>160</v>
@@ -15819,7 +15831,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15828,10 +15840,10 @@
         <v>55</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>95</v>
@@ -15841,7 +15853,7 @@
       </c>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15856,13 +15868,13 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>55</v>
@@ -15878,7 +15890,7 @@
       </c>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>503</v>
+        <v>72</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15908,7 +15920,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15923,7 +15935,7 @@
         <v>468</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15943,7 +15955,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15958,12 +15970,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15978,7 +15990,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -16013,7 +16025,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -16025,14 +16037,16 @@
         <v>22</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>24</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
-      <c r="M450" s="7"/>
+      <c t="s" r="M450" s="7">
+        <v>503</v>
+      </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
       <c t="s" r="A451" s="6">
@@ -16046,7 +16060,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -16061,7 +16075,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16094,7 +16108,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16114,7 +16128,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16129,7 +16143,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16149,7 +16163,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16164,7 +16178,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16179,14 +16193,14 @@
         <v>108</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="K455" s="7">
         <v>128</v>
       </c>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16201,7 +16215,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -16223,7 +16237,7 @@
       </c>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>135</v>
+        <v>508</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -16238,7 +16252,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16247,7 +16261,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>223</v>
@@ -16271,13 +16285,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>55</v>
@@ -16482,10 +16496,10 @@
         <v>516</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -16568,7 +16582,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -16616,7 +16630,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -16684,7 +16698,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -16847,7 +16861,7 @@
         <v>525</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>122</v>
@@ -16882,10 +16896,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
